--- a/src/report/assets/pbs_dev_base.xlsx
+++ b/src/report/assets/pbs_dev_base.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0_ "/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -97,8 +97,32 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="FFFF0000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -139,6 +163,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,7 +260,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
@@ -379,17 +413,74 @@
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -649,33 +740,33 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.99609375" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.62" customWidth="1" style="28" min="1" max="1"/>
-    <col width="23.29" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10.69" customWidth="1" style="28" min="3" max="3"/>
-    <col width="13.74" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10.69" customWidth="1" style="28" min="5" max="6"/>
-    <col width="8.99" customWidth="1" style="28" min="7" max="236"/>
+    <col width="23.3" customWidth="1" style="28" min="2" max="2"/>
+    <col width="10.7" customWidth="1" style="28" min="3" max="3"/>
+    <col width="13.75" customWidth="1" style="28" min="4" max="4"/>
+    <col width="10.7" customWidth="1" style="28" min="5" max="6"/>
+    <col width="10.7" customWidth="1" style="29" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" s="29"/>
     <row r="2" ht="40" customFormat="1" customHeight="1" s="28">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="54" t="inlineStr">
         <is>
           <t>阜阳分行网点私人银行客户发展情况表（  年  月  日）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>支行</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="72" t="inlineStr">
         <is>
           <t>网点</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="72" t="inlineStr">
         <is>
           <t>月日均600万以上客户</t>
         </is>
@@ -687,22 +778,22 @@
     <row r="4" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="35" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>当前存量客户</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="72" t="inlineStr">
         <is>
           <t>上年末</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>较年初</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="72" t="inlineStr">
         <is>
           <t>本年增幅</t>
         </is>
@@ -717,624 +808,624 @@
       <c r="F5" s="37" t="n"/>
     </row>
     <row r="6" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="73" t="inlineStr">
         <is>
           <t>颍州</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>阜阳颍州支行营业室</t>
         </is>
       </c>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="39" t="n"/>
-      <c r="F6" s="40" t="n"/>
+      <c r="C6" s="74" t="n"/>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="75" t="n"/>
+      <c r="F6" s="76" t="n"/>
     </row>
     <row r="7" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A7" s="35" t="n"/>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>阜阳金鹰支行</t>
         </is>
       </c>
-      <c r="C7" s="38" t="n"/>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="39" t="n"/>
-      <c r="F7" s="40" t="n"/>
+      <c r="C7" s="74" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="75" t="n"/>
+      <c r="F7" s="76" t="n"/>
     </row>
     <row r="8" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A8" s="35" t="n"/>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>阜阳南站支行</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="39" t="n"/>
-      <c r="F8" s="40" t="n"/>
+      <c r="C8" s="74" t="n"/>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="76" t="n"/>
     </row>
     <row r="9" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A9" s="35" t="n"/>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>阜阳清河支行</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n"/>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="39" t="n"/>
-      <c r="F9" s="40" t="n"/>
+      <c r="C9" s="74" t="n"/>
+      <c r="D9" s="74" t="n"/>
+      <c r="E9" s="75" t="n"/>
+      <c r="F9" s="76" t="n"/>
     </row>
     <row r="10" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A10" s="35" t="n"/>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>阜阳师范大学支行</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="39" t="n"/>
-      <c r="F10" s="40" t="n"/>
+      <c r="C10" s="74" t="n"/>
+      <c r="D10" s="74" t="n"/>
+      <c r="E10" s="75" t="n"/>
+      <c r="F10" s="76" t="n"/>
     </row>
     <row r="11" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A11" s="35" t="n"/>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>阜阳城建支行</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="39" t="n"/>
-      <c r="F11" s="40" t="n"/>
+      <c r="C11" s="74" t="n"/>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="75" t="n"/>
+      <c r="F11" s="76" t="n"/>
     </row>
     <row r="12" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A12" s="35" t="n"/>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>阜阳文峰支行</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="40" t="n"/>
+      <c r="C12" s="74" t="n"/>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="75" t="n"/>
+      <c r="F12" s="76" t="n"/>
     </row>
     <row r="13" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A13" s="37" t="n"/>
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="45" t="n"/>
+      <c r="C13" s="63" t="n"/>
+      <c r="D13" s="63" t="n"/>
+      <c r="E13" s="64" t="n"/>
+      <c r="F13" s="65" t="n"/>
     </row>
     <row r="14" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="73" t="inlineStr">
         <is>
           <t>颍泉</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="74" t="inlineStr">
         <is>
           <t>阜阳颍泉支行营业室</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="39" t="n"/>
-      <c r="F14" s="40" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="75" t="n"/>
+      <c r="F14" s="76" t="n"/>
     </row>
     <row r="15" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A15" s="35" t="n"/>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>阜阳临沂商城支行</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="39" t="n"/>
-      <c r="F15" s="40" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="75" t="n"/>
+      <c r="F15" s="76" t="n"/>
     </row>
     <row r="16" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A16" s="35" t="n"/>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="74" t="inlineStr">
         <is>
           <t>阜阳瑶海支行</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="39" t="n"/>
-      <c r="F16" s="40" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="75" t="n"/>
+      <c r="F16" s="76" t="n"/>
     </row>
     <row r="17" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A17" s="35" t="n"/>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="74" t="inlineStr">
         <is>
           <t>阜阳人民路支行</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="39" t="n"/>
-      <c r="F17" s="40" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="75" t="n"/>
+      <c r="F17" s="76" t="n"/>
     </row>
     <row r="18" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A18" s="35" t="n"/>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="74" t="inlineStr">
         <is>
           <t>阜阳大楼支行</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="39" t="n"/>
-      <c r="F18" s="40" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="76" t="n"/>
     </row>
     <row r="19" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A19" s="35" t="n"/>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="74" t="inlineStr">
         <is>
           <t>阜阳小隅首支行</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="46" t="n"/>
-      <c r="F19" s="40" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="75" t="n"/>
+      <c r="F19" s="76" t="n"/>
     </row>
     <row r="20" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A20" s="35" t="n"/>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="74" t="inlineStr">
         <is>
           <t>阜阳牡丹支行</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="39" t="n"/>
-      <c r="F20" s="40" t="n"/>
+      <c r="C20" s="74" t="n"/>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="75" t="n"/>
+      <c r="F20" s="76" t="n"/>
     </row>
     <row r="21" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A21" s="37" t="n"/>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C21" s="43" t="n"/>
-      <c r="D21" s="43" t="n"/>
-      <c r="E21" s="44" t="n"/>
-      <c r="F21" s="45" t="n"/>
+      <c r="C21" s="63" t="n"/>
+      <c r="D21" s="63" t="n"/>
+      <c r="E21" s="64" t="n"/>
+      <c r="F21" s="65" t="n"/>
     </row>
     <row r="22" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="73" t="inlineStr">
         <is>
           <t>颍东</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="74" t="inlineStr">
         <is>
           <t>阜阳颍河支行</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="46" t="n"/>
-      <c r="F22" s="40" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="75" t="n"/>
+      <c r="F22" s="76" t="n"/>
     </row>
     <row r="23" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A23" s="35" t="n"/>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="74" t="inlineStr">
         <is>
           <t>阜阳颍东支行营业室</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n"/>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="46" t="n"/>
-      <c r="F23" s="40" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="75" t="n"/>
+      <c r="F23" s="76" t="n"/>
     </row>
     <row r="24" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A24" s="35" t="n"/>
-      <c r="B24" s="41" t="inlineStr">
+      <c r="B24" s="74" t="inlineStr">
         <is>
           <t>阜阳青年支行</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="38" t="n"/>
-      <c r="E24" s="46" t="n"/>
-      <c r="F24" s="40" t="n"/>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="75" t="n"/>
+      <c r="F24" s="76" t="n"/>
     </row>
     <row r="25" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A25" s="35" t="n"/>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="74" t="inlineStr">
         <is>
           <t>阜阳烟厂支行</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="38" t="n"/>
-      <c r="E25" s="46" t="n"/>
-      <c r="F25" s="40" t="n"/>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="75" t="n"/>
+      <c r="F25" s="76" t="n"/>
     </row>
     <row r="26" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A26" s="35" t="n"/>
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B26" s="74" t="inlineStr">
         <is>
           <t>阜阳岳家湖支行</t>
         </is>
       </c>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="38" t="n"/>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="40" t="n"/>
+      <c r="C26" s="74" t="n"/>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="75" t="n"/>
+      <c r="F26" s="76" t="n"/>
     </row>
     <row r="27" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A27" s="35" t="n"/>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="74" t="inlineStr">
         <is>
           <t>阜阳汇通支行</t>
         </is>
       </c>
-      <c r="C27" s="48" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="39" t="n"/>
-      <c r="F27" s="40" t="n"/>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="75" t="n"/>
+      <c r="F27" s="76" t="n"/>
     </row>
     <row r="28" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A28" s="37" t="n"/>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="43" t="n"/>
-      <c r="E28" s="44" t="n"/>
-      <c r="F28" s="45" t="n"/>
+      <c r="C28" s="63" t="n"/>
+      <c r="D28" s="63" t="n"/>
+      <c r="E28" s="64" t="n"/>
+      <c r="F28" s="65" t="n"/>
     </row>
     <row r="29" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="73" t="inlineStr">
         <is>
           <t>界首</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="74" t="inlineStr">
         <is>
           <t>阜阳界首支行营业室</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="38" t="n"/>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="40" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="75" t="n"/>
+      <c r="F29" s="76" t="n"/>
     </row>
     <row r="30" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A30" s="35" t="n"/>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="74" t="inlineStr">
         <is>
           <t>阜阳界首城建支行</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="38" t="n"/>
-      <c r="E30" s="46" t="n"/>
-      <c r="F30" s="40" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="75" t="n"/>
+      <c r="F30" s="76" t="n"/>
     </row>
     <row r="31" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A31" s="35" t="n"/>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B31" s="74" t="inlineStr">
         <is>
           <t>阜阳界首科创支行</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="46" t="n"/>
-      <c r="F31" s="40" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="75" t="n"/>
+      <c r="F31" s="76" t="n"/>
     </row>
     <row r="32" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A32" s="35" t="n"/>
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>阜阳界首新街口支行</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="46" t="n"/>
-      <c r="F32" s="40" t="n"/>
+      <c r="C32" s="74" t="n"/>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="75" t="n"/>
+      <c r="F32" s="76" t="n"/>
     </row>
     <row r="33" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A33" s="37" t="n"/>
-      <c r="B33" s="42" t="inlineStr">
+      <c r="B33" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="43" t="n"/>
-      <c r="E33" s="44" t="n"/>
-      <c r="F33" s="45" t="n"/>
+      <c r="C33" s="63" t="n"/>
+      <c r="D33" s="63" t="n"/>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="65" t="n"/>
     </row>
     <row r="34" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="73" t="inlineStr">
         <is>
           <t>临泉</t>
         </is>
       </c>
-      <c r="B34" s="41" t="inlineStr">
+      <c r="B34" s="74" t="inlineStr">
         <is>
           <t>阜阳临泉支行营业室</t>
         </is>
       </c>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="39" t="n"/>
-      <c r="F34" s="40" t="n"/>
+      <c r="C34" s="74" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="75" t="n"/>
+      <c r="F34" s="76" t="n"/>
     </row>
     <row r="35" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A35" s="35" t="n"/>
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B35" s="74" t="inlineStr">
         <is>
           <t>阜阳临泉文明支行</t>
         </is>
       </c>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="38" t="n"/>
-      <c r="E35" s="39" t="n"/>
-      <c r="F35" s="40" t="n"/>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="75" t="n"/>
+      <c r="F35" s="76" t="n"/>
     </row>
     <row r="36" ht="20" customFormat="1" customHeight="1" s="49">
       <c r="A36" s="35" t="n"/>
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B36" s="74" t="inlineStr">
         <is>
           <t>阜阳临泉政务新区支行</t>
         </is>
       </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="38" t="n"/>
-      <c r="E36" s="39" t="n"/>
-      <c r="F36" s="40" t="n"/>
+      <c r="C36" s="74" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="76" t="n"/>
     </row>
     <row r="37" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A37" s="35" t="n"/>
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B37" s="74" t="inlineStr">
         <is>
           <t>阜阳临泉姜尚支行</t>
         </is>
       </c>
-      <c r="C37" s="38" t="n"/>
-      <c r="D37" s="38" t="n"/>
-      <c r="E37" s="39" t="n"/>
-      <c r="F37" s="40" t="n"/>
+      <c r="C37" s="74" t="n"/>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="75" t="n"/>
+      <c r="F37" s="76" t="n"/>
     </row>
     <row r="38" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A38" s="37" t="n"/>
-      <c r="B38" s="42" t="inlineStr">
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C38" s="43" t="n"/>
-      <c r="D38" s="43" t="n"/>
-      <c r="E38" s="44" t="n"/>
-      <c r="F38" s="45" t="n"/>
+      <c r="C38" s="63" t="n"/>
+      <c r="D38" s="63" t="n"/>
+      <c r="E38" s="64" t="n"/>
+      <c r="F38" s="65" t="n"/>
     </row>
     <row r="39" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="73" t="inlineStr">
         <is>
           <t>阜南</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B39" s="74" t="inlineStr">
         <is>
           <t>阜阳阜南支行营业室</t>
         </is>
       </c>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="46" t="n"/>
-      <c r="F39" s="40" t="n"/>
+      <c r="C39" s="74" t="n"/>
+      <c r="D39" s="74" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="76" t="n"/>
     </row>
     <row r="40" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A40" s="35" t="n"/>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B40" s="74" t="inlineStr">
         <is>
           <t>阜阳阜南百货大楼支行</t>
         </is>
       </c>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="46" t="n"/>
-      <c r="F40" s="40" t="n"/>
+      <c r="C40" s="74" t="n"/>
+      <c r="D40" s="74" t="n"/>
+      <c r="E40" s="75" t="n"/>
+      <c r="F40" s="76" t="n"/>
     </row>
     <row r="41" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A41" s="35" t="n"/>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B41" s="74" t="inlineStr">
         <is>
           <t>阜阳阜南北城支行</t>
         </is>
       </c>
-      <c r="C41" s="38" t="n"/>
-      <c r="D41" s="38" t="n"/>
-      <c r="E41" s="46" t="n"/>
-      <c r="F41" s="40" t="n"/>
+      <c r="C41" s="74" t="n"/>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="75" t="n"/>
+      <c r="F41" s="76" t="n"/>
     </row>
     <row r="42" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A42" s="35" t="n"/>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B42" s="74" t="inlineStr">
         <is>
           <t>阜阳阜南胜利路支行</t>
         </is>
       </c>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="38" t="n"/>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="40" t="n"/>
+      <c r="C42" s="74" t="n"/>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="75" t="n"/>
+      <c r="F42" s="76" t="n"/>
     </row>
     <row r="43" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A43" s="37" t="n"/>
-      <c r="B43" s="42" t="inlineStr">
+      <c r="B43" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="44" t="n"/>
-      <c r="F43" s="45" t="n"/>
+      <c r="C43" s="63" t="n"/>
+      <c r="D43" s="63" t="n"/>
+      <c r="E43" s="64" t="n"/>
+      <c r="F43" s="65" t="n"/>
     </row>
     <row r="44" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="A44" s="73" t="inlineStr">
         <is>
           <t>颍上</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B44" s="74" t="inlineStr">
         <is>
           <t>阜阳颍上支行营业室</t>
         </is>
       </c>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="46" t="n"/>
-      <c r="F44" s="40" t="n"/>
+      <c r="C44" s="74" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="75" t="n"/>
+      <c r="F44" s="76" t="n"/>
     </row>
     <row r="45" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A45" s="35" t="n"/>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B45" s="74" t="inlineStr">
         <is>
           <t>阜阳颍上北关支行</t>
         </is>
       </c>
-      <c r="C45" s="38" t="n"/>
-      <c r="D45" s="38" t="n"/>
-      <c r="E45" s="39" t="n"/>
-      <c r="F45" s="40" t="n"/>
+      <c r="C45" s="74" t="n"/>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="75" t="n"/>
+      <c r="F45" s="76" t="n"/>
     </row>
     <row r="46" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A46" s="35" t="n"/>
-      <c r="B46" s="41" t="inlineStr">
+      <c r="B46" s="74" t="inlineStr">
         <is>
           <t>阜阳颍上十字街支行</t>
         </is>
       </c>
-      <c r="C46" s="47" t="n"/>
-      <c r="D46" s="38" t="n"/>
-      <c r="E46" s="39" t="n"/>
-      <c r="F46" s="40" t="n"/>
+      <c r="C46" s="74" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="75" t="n"/>
+      <c r="F46" s="76" t="n"/>
     </row>
     <row r="47" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A47" s="35" t="n"/>
-      <c r="B47" s="41" t="inlineStr">
+      <c r="B47" s="74" t="inlineStr">
         <is>
           <t>阜阳颍上管仲支行</t>
         </is>
       </c>
-      <c r="C47" s="38" t="n"/>
-      <c r="D47" s="38" t="n"/>
-      <c r="E47" s="39" t="n"/>
-      <c r="F47" s="40" t="n"/>
+      <c r="C47" s="74" t="n"/>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="75" t="n"/>
+      <c r="F47" s="76" t="n"/>
     </row>
     <row r="48" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A48" s="37" t="n"/>
-      <c r="B48" s="42" t="inlineStr">
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="44" t="n"/>
-      <c r="F48" s="45" t="n"/>
+      <c r="C48" s="63" t="n"/>
+      <c r="D48" s="63" t="n"/>
+      <c r="E48" s="64" t="n"/>
+      <c r="F48" s="65" t="n"/>
     </row>
     <row r="49" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="73" t="inlineStr">
         <is>
           <t>太和</t>
         </is>
       </c>
-      <c r="B49" s="41" t="inlineStr">
+      <c r="B49" s="74" t="inlineStr">
         <is>
           <t>阜阳太和支行营业室</t>
         </is>
       </c>
-      <c r="C49" s="38" t="n"/>
-      <c r="D49" s="38" t="n"/>
-      <c r="E49" s="46" t="n"/>
-      <c r="F49" s="40" t="n"/>
+      <c r="C49" s="74" t="n"/>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="75" t="n"/>
+      <c r="F49" s="76" t="n"/>
     </row>
     <row r="50" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A50" s="35" t="n"/>
-      <c r="B50" s="41" t="inlineStr">
+      <c r="B50" s="74" t="inlineStr">
         <is>
           <t>阜阳太和人民路支行</t>
         </is>
       </c>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="38" t="n"/>
-      <c r="E50" s="39" t="n"/>
-      <c r="F50" s="40" t="n"/>
+      <c r="C50" s="74" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="75" t="n"/>
+      <c r="F50" s="76" t="n"/>
     </row>
     <row r="51" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A51" s="35" t="n"/>
-      <c r="B51" s="41" t="inlineStr">
+      <c r="B51" s="74" t="inlineStr">
         <is>
           <t>阜阳太和大桥支行</t>
         </is>
       </c>
-      <c r="C51" s="38" t="n"/>
-      <c r="D51" s="38" t="n"/>
-      <c r="E51" s="39" t="n"/>
-      <c r="F51" s="40" t="n"/>
+      <c r="C51" s="74" t="n"/>
+      <c r="D51" s="74" t="n"/>
+      <c r="E51" s="75" t="n"/>
+      <c r="F51" s="76" t="n"/>
     </row>
     <row r="52" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A52" s="35" t="n"/>
-      <c r="B52" s="41" t="inlineStr">
+      <c r="B52" s="74" t="inlineStr">
         <is>
           <t>阜阳太和华源支行</t>
         </is>
       </c>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="38" t="n"/>
-      <c r="E52" s="39" t="n"/>
-      <c r="F52" s="40" t="n"/>
+      <c r="C52" s="74" t="n"/>
+      <c r="D52" s="74" t="n"/>
+      <c r="E52" s="75" t="n"/>
+      <c r="F52" s="76" t="n"/>
     </row>
     <row r="53" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A53" s="37" t="n"/>
-      <c r="B53" s="42" t="inlineStr">
+      <c r="B53" s="62" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="43" t="n"/>
-      <c r="E53" s="44" t="n"/>
-      <c r="F53" s="45" t="n"/>
+      <c r="C53" s="63" t="n"/>
+      <c r="D53" s="63" t="n"/>
+      <c r="E53" s="64" t="n"/>
+      <c r="F53" s="65" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="29">
-      <c r="A54" s="50" t="inlineStr">
+      <c r="A54" s="74" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
       <c r="B54" s="34" t="n"/>
-      <c r="C54" s="51" t="n"/>
-      <c r="D54" s="51" t="n"/>
-      <c r="E54" s="52" t="n"/>
-      <c r="F54" s="53" t="n"/>
+      <c r="C54" s="74" t="n"/>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="75" t="n"/>
+      <c r="F54" s="76" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">

--- a/src/report/assets/pbs_dev_base.xlsx
+++ b/src/report/assets/pbs_dev_base.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0_ "/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="12">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -97,32 +97,8 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="FFFF0000"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -163,16 +139,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
         <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -260,7 +226,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
@@ -411,75 +377,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,33 +637,33 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.99609375" defaultRowHeight="15.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.62" customWidth="1" style="28" min="1" max="1"/>
-    <col width="23.3" customWidth="1" style="28" min="2" max="2"/>
-    <col width="10.7" customWidth="1" style="28" min="3" max="3"/>
-    <col width="13.75" customWidth="1" style="28" min="4" max="4"/>
-    <col width="10.7" customWidth="1" style="28" min="5" max="6"/>
-    <col width="10.7" customWidth="1" style="29" min="6" max="6"/>
+    <col width="23.29" customWidth="1" style="28" min="2" max="2"/>
+    <col width="10.69" customWidth="1" style="28" min="3" max="3"/>
+    <col width="13.74" customWidth="1" style="28" min="4" max="4"/>
+    <col width="10.69" customWidth="1" style="28" min="5" max="6"/>
+    <col width="8.99" customWidth="1" style="28" min="7" max="236"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" s="29"/>
     <row r="2" ht="40" customFormat="1" customHeight="1" s="28">
-      <c r="A2" s="54" t="inlineStr">
-        <is>
-          <t>阜阳分行网点私人银行客户发展情况表（  年  月  日）</t>
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>阜阳分行网点私人银行客户发展情况表（2026年10月24日）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>支行</t>
         </is>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>网点</t>
         </is>
       </c>
-      <c r="C3" s="72" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>月日均600万以上客户</t>
         </is>
@@ -778,22 +675,20 @@
     <row r="4" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A4" s="35" t="n"/>
       <c r="B4" s="35" t="n"/>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>当前存量客户</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
-        <is>
-          <t>上年末</t>
-        </is>
-      </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="D4" s="36" t="n">
+        <v>202512</v>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>较年初</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
         <is>
           <t>本年增幅</t>
         </is>
@@ -808,624 +703,624 @@
       <c r="F5" s="37" t="n"/>
     </row>
     <row r="6" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A6" s="73" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>颍州</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>阜阳颍州支行营业室</t>
         </is>
       </c>
-      <c r="C6" s="74" t="n"/>
-      <c r="D6" s="74" t="n"/>
-      <c r="E6" s="75" t="n"/>
-      <c r="F6" s="76" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="40" t="n"/>
     </row>
     <row r="7" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A7" s="35" t="n"/>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>阜阳金鹰支行</t>
         </is>
       </c>
-      <c r="C7" s="74" t="n"/>
-      <c r="D7" s="74" t="n"/>
-      <c r="E7" s="75" t="n"/>
-      <c r="F7" s="76" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="40" t="n"/>
     </row>
     <row r="8" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A8" s="35" t="n"/>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>阜阳南站支行</t>
         </is>
       </c>
-      <c r="C8" s="74" t="n"/>
-      <c r="D8" s="74" t="n"/>
-      <c r="E8" s="75" t="n"/>
-      <c r="F8" s="76" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="40" t="n"/>
     </row>
     <row r="9" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A9" s="35" t="n"/>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>阜阳清河支行</t>
         </is>
       </c>
-      <c r="C9" s="74" t="n"/>
-      <c r="D9" s="74" t="n"/>
-      <c r="E9" s="75" t="n"/>
-      <c r="F9" s="76" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="40" t="n"/>
     </row>
     <row r="10" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A10" s="35" t="n"/>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>阜阳师范大学支行</t>
         </is>
       </c>
-      <c r="C10" s="74" t="n"/>
-      <c r="D10" s="74" t="n"/>
-      <c r="E10" s="75" t="n"/>
-      <c r="F10" s="76" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="40" t="n"/>
     </row>
     <row r="11" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A11" s="35" t="n"/>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>阜阳城建支行</t>
         </is>
       </c>
-      <c r="C11" s="74" t="n"/>
-      <c r="D11" s="74" t="n"/>
-      <c r="E11" s="75" t="n"/>
-      <c r="F11" s="76" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A12" s="35" t="n"/>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>阜阳文峰支行</t>
         </is>
       </c>
-      <c r="C12" s="74" t="n"/>
-      <c r="D12" s="74" t="n"/>
-      <c r="E12" s="75" t="n"/>
-      <c r="F12" s="76" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="40" t="n"/>
     </row>
     <row r="13" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A13" s="37" t="n"/>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C13" s="63" t="n"/>
-      <c r="D13" s="63" t="n"/>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="65" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="45" t="n"/>
     </row>
     <row r="14" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A14" s="73" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>颍泉</t>
         </is>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>阜阳颍泉支行营业室</t>
         </is>
       </c>
-      <c r="C14" s="74" t="n"/>
-      <c r="D14" s="74" t="n"/>
-      <c r="E14" s="75" t="n"/>
-      <c r="F14" s="76" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="40" t="n"/>
     </row>
     <row r="15" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A15" s="35" t="n"/>
-      <c r="B15" s="74" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>阜阳临沂商城支行</t>
         </is>
       </c>
-      <c r="C15" s="74" t="n"/>
-      <c r="D15" s="74" t="n"/>
-      <c r="E15" s="75" t="n"/>
-      <c r="F15" s="76" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="40" t="n"/>
     </row>
     <row r="16" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A16" s="35" t="n"/>
-      <c r="B16" s="74" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>阜阳瑶海支行</t>
         </is>
       </c>
-      <c r="C16" s="74" t="n"/>
-      <c r="D16" s="74" t="n"/>
-      <c r="E16" s="75" t="n"/>
-      <c r="F16" s="76" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="40" t="n"/>
     </row>
     <row r="17" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A17" s="35" t="n"/>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>阜阳人民路支行</t>
         </is>
       </c>
-      <c r="C17" s="74" t="n"/>
-      <c r="D17" s="74" t="n"/>
-      <c r="E17" s="75" t="n"/>
-      <c r="F17" s="76" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="40" t="n"/>
     </row>
     <row r="18" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A18" s="35" t="n"/>
-      <c r="B18" s="74" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>阜阳大楼支行</t>
         </is>
       </c>
-      <c r="C18" s="74" t="n"/>
-      <c r="D18" s="74" t="n"/>
-      <c r="E18" s="75" t="n"/>
-      <c r="F18" s="76" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="40" t="n"/>
     </row>
     <row r="19" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A19" s="35" t="n"/>
-      <c r="B19" s="74" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>阜阳小隅首支行</t>
         </is>
       </c>
-      <c r="C19" s="74" t="n"/>
-      <c r="D19" s="74" t="n"/>
-      <c r="E19" s="75" t="n"/>
-      <c r="F19" s="76" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="40" t="n"/>
     </row>
     <row r="20" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A20" s="35" t="n"/>
-      <c r="B20" s="74" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>阜阳牡丹支行</t>
         </is>
       </c>
-      <c r="C20" s="74" t="n"/>
-      <c r="D20" s="74" t="n"/>
-      <c r="E20" s="75" t="n"/>
-      <c r="F20" s="76" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="40" t="n"/>
     </row>
     <row r="21" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A21" s="37" t="n"/>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C21" s="63" t="n"/>
-      <c r="D21" s="63" t="n"/>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="65" t="n"/>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="45" t="n"/>
     </row>
     <row r="22" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A22" s="73" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>颍东</t>
         </is>
       </c>
-      <c r="B22" s="74" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>阜阳颍河支行</t>
         </is>
       </c>
-      <c r="C22" s="74" t="n"/>
-      <c r="D22" s="74" t="n"/>
-      <c r="E22" s="75" t="n"/>
-      <c r="F22" s="76" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="E22" s="46" t="n"/>
+      <c r="F22" s="40" t="n"/>
     </row>
     <row r="23" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A23" s="35" t="n"/>
-      <c r="B23" s="74" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>阜阳颍东支行营业室</t>
         </is>
       </c>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="75" t="n"/>
-      <c r="F23" s="76" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="38" t="n"/>
+      <c r="E23" s="46" t="n"/>
+      <c r="F23" s="40" t="n"/>
     </row>
     <row r="24" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A24" s="35" t="n"/>
-      <c r="B24" s="74" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>阜阳青年支行</t>
         </is>
       </c>
-      <c r="C24" s="74" t="n"/>
-      <c r="D24" s="74" t="n"/>
-      <c r="E24" s="75" t="n"/>
-      <c r="F24" s="76" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="46" t="n"/>
+      <c r="F24" s="40" t="n"/>
     </row>
     <row r="25" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A25" s="35" t="n"/>
-      <c r="B25" s="74" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>阜阳烟厂支行</t>
         </is>
       </c>
-      <c r="C25" s="74" t="n"/>
-      <c r="D25" s="74" t="n"/>
-      <c r="E25" s="75" t="n"/>
-      <c r="F25" s="76" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="E25" s="46" t="n"/>
+      <c r="F25" s="40" t="n"/>
     </row>
     <row r="26" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A26" s="35" t="n"/>
-      <c r="B26" s="74" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>阜阳岳家湖支行</t>
         </is>
       </c>
-      <c r="C26" s="74" t="n"/>
-      <c r="D26" s="74" t="n"/>
-      <c r="E26" s="75" t="n"/>
-      <c r="F26" s="76" t="n"/>
+      <c r="C26" s="47" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="46" t="n"/>
+      <c r="F26" s="40" t="n"/>
     </row>
     <row r="27" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A27" s="35" t="n"/>
-      <c r="B27" s="74" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>阜阳汇通支行</t>
         </is>
       </c>
-      <c r="C27" s="74" t="n"/>
-      <c r="D27" s="74" t="n"/>
-      <c r="E27" s="75" t="n"/>
-      <c r="F27" s="76" t="n"/>
+      <c r="C27" s="48" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="40" t="n"/>
     </row>
     <row r="28" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A28" s="37" t="n"/>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C28" s="63" t="n"/>
-      <c r="D28" s="63" t="n"/>
-      <c r="E28" s="64" t="n"/>
-      <c r="F28" s="65" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="45" t="n"/>
     </row>
     <row r="29" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A29" s="73" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>界首</t>
         </is>
       </c>
-      <c r="B29" s="74" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>阜阳界首支行营业室</t>
         </is>
       </c>
-      <c r="C29" s="74" t="n"/>
-      <c r="D29" s="74" t="n"/>
-      <c r="E29" s="75" t="n"/>
-      <c r="F29" s="76" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="E29" s="46" t="n"/>
+      <c r="F29" s="40" t="n"/>
     </row>
     <row r="30" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A30" s="35" t="n"/>
-      <c r="B30" s="74" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>阜阳界首城建支行</t>
         </is>
       </c>
-      <c r="C30" s="74" t="n"/>
-      <c r="D30" s="74" t="n"/>
-      <c r="E30" s="75" t="n"/>
-      <c r="F30" s="76" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="E30" s="46" t="n"/>
+      <c r="F30" s="40" t="n"/>
     </row>
     <row r="31" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A31" s="35" t="n"/>
-      <c r="B31" s="74" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>阜阳界首科创支行</t>
         </is>
       </c>
-      <c r="C31" s="74" t="n"/>
-      <c r="D31" s="74" t="n"/>
-      <c r="E31" s="75" t="n"/>
-      <c r="F31" s="76" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="E31" s="46" t="n"/>
+      <c r="F31" s="40" t="n"/>
     </row>
     <row r="32" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A32" s="35" t="n"/>
-      <c r="B32" s="74" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>阜阳界首新街口支行</t>
         </is>
       </c>
-      <c r="C32" s="74" t="n"/>
-      <c r="D32" s="74" t="n"/>
-      <c r="E32" s="75" t="n"/>
-      <c r="F32" s="76" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="E32" s="46" t="n"/>
+      <c r="F32" s="40" t="n"/>
     </row>
     <row r="33" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A33" s="37" t="n"/>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="B33" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C33" s="63" t="n"/>
-      <c r="D33" s="63" t="n"/>
-      <c r="E33" s="64" t="n"/>
-      <c r="F33" s="65" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="44" t="n"/>
+      <c r="F33" s="45" t="n"/>
     </row>
     <row r="34" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A34" s="73" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>临泉</t>
         </is>
       </c>
-      <c r="B34" s="74" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>阜阳临泉支行营业室</t>
         </is>
       </c>
-      <c r="C34" s="74" t="n"/>
-      <c r="D34" s="74" t="n"/>
-      <c r="E34" s="75" t="n"/>
-      <c r="F34" s="76" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="40" t="n"/>
     </row>
     <row r="35" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A35" s="35" t="n"/>
-      <c r="B35" s="74" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>阜阳临泉文明支行</t>
         </is>
       </c>
-      <c r="C35" s="74" t="n"/>
-      <c r="D35" s="74" t="n"/>
-      <c r="E35" s="75" t="n"/>
-      <c r="F35" s="76" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="40" t="n"/>
     </row>
     <row r="36" ht="20" customFormat="1" customHeight="1" s="49">
       <c r="A36" s="35" t="n"/>
-      <c r="B36" s="74" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>阜阳临泉政务新区支行</t>
         </is>
       </c>
-      <c r="C36" s="74" t="n"/>
-      <c r="D36" s="74" t="n"/>
-      <c r="E36" s="75" t="n"/>
-      <c r="F36" s="76" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="40" t="n"/>
     </row>
     <row r="37" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A37" s="35" t="n"/>
-      <c r="B37" s="74" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>阜阳临泉姜尚支行</t>
         </is>
       </c>
-      <c r="C37" s="74" t="n"/>
-      <c r="D37" s="74" t="n"/>
-      <c r="E37" s="75" t="n"/>
-      <c r="F37" s="76" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="40" t="n"/>
     </row>
     <row r="38" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A38" s="37" t="n"/>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="B38" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C38" s="63" t="n"/>
-      <c r="D38" s="63" t="n"/>
-      <c r="E38" s="64" t="n"/>
-      <c r="F38" s="65" t="n"/>
+      <c r="C38" s="43" t="n"/>
+      <c r="D38" s="43" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="45" t="n"/>
     </row>
     <row r="39" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A39" s="73" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t>阜南</t>
         </is>
       </c>
-      <c r="B39" s="74" t="inlineStr">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>阜阳阜南支行营业室</t>
         </is>
       </c>
-      <c r="C39" s="74" t="n"/>
-      <c r="D39" s="74" t="n"/>
-      <c r="E39" s="75" t="n"/>
-      <c r="F39" s="76" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="46" t="n"/>
+      <c r="F39" s="40" t="n"/>
     </row>
     <row r="40" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A40" s="35" t="n"/>
-      <c r="B40" s="74" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>阜阳阜南百货大楼支行</t>
         </is>
       </c>
-      <c r="C40" s="74" t="n"/>
-      <c r="D40" s="74" t="n"/>
-      <c r="E40" s="75" t="n"/>
-      <c r="F40" s="76" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="46" t="n"/>
+      <c r="F40" s="40" t="n"/>
     </row>
     <row r="41" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A41" s="35" t="n"/>
-      <c r="B41" s="74" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>阜阳阜南北城支行</t>
         </is>
       </c>
-      <c r="C41" s="74" t="n"/>
-      <c r="D41" s="74" t="n"/>
-      <c r="E41" s="75" t="n"/>
-      <c r="F41" s="76" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="46" t="n"/>
+      <c r="F41" s="40" t="n"/>
     </row>
     <row r="42" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A42" s="35" t="n"/>
-      <c r="B42" s="74" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>阜阳阜南胜利路支行</t>
         </is>
       </c>
-      <c r="C42" s="74" t="n"/>
-      <c r="D42" s="74" t="n"/>
-      <c r="E42" s="75" t="n"/>
-      <c r="F42" s="76" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="38" t="n"/>
+      <c r="E42" s="46" t="n"/>
+      <c r="F42" s="40" t="n"/>
     </row>
     <row r="43" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A43" s="37" t="n"/>
-      <c r="B43" s="62" t="inlineStr">
+      <c r="B43" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C43" s="63" t="n"/>
-      <c r="D43" s="63" t="n"/>
-      <c r="E43" s="64" t="n"/>
-      <c r="F43" s="65" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="43" t="n"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="45" t="n"/>
     </row>
     <row r="44" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A44" s="73" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>颍上</t>
         </is>
       </c>
-      <c r="B44" s="74" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>阜阳颍上支行营业室</t>
         </is>
       </c>
-      <c r="C44" s="74" t="n"/>
-      <c r="D44" s="74" t="n"/>
-      <c r="E44" s="75" t="n"/>
-      <c r="F44" s="76" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="46" t="n"/>
+      <c r="F44" s="40" t="n"/>
     </row>
     <row r="45" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A45" s="35" t="n"/>
-      <c r="B45" s="74" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>阜阳颍上北关支行</t>
         </is>
       </c>
-      <c r="C45" s="74" t="n"/>
-      <c r="D45" s="74" t="n"/>
-      <c r="E45" s="75" t="n"/>
-      <c r="F45" s="76" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="40" t="n"/>
     </row>
     <row r="46" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A46" s="35" t="n"/>
-      <c r="B46" s="74" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>阜阳颍上十字街支行</t>
         </is>
       </c>
-      <c r="C46" s="74" t="n"/>
-      <c r="D46" s="74" t="n"/>
-      <c r="E46" s="75" t="n"/>
-      <c r="F46" s="76" t="n"/>
+      <c r="C46" s="47" t="n"/>
+      <c r="D46" s="38" t="n"/>
+      <c r="E46" s="39" t="n"/>
+      <c r="F46" s="40" t="n"/>
     </row>
     <row r="47" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A47" s="35" t="n"/>
-      <c r="B47" s="74" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>阜阳颍上管仲支行</t>
         </is>
       </c>
-      <c r="C47" s="74" t="n"/>
-      <c r="D47" s="74" t="n"/>
-      <c r="E47" s="75" t="n"/>
-      <c r="F47" s="76" t="n"/>
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="38" t="n"/>
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="40" t="n"/>
     </row>
     <row r="48" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A48" s="37" t="n"/>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="B48" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C48" s="63" t="n"/>
-      <c r="D48" s="63" t="n"/>
-      <c r="E48" s="64" t="n"/>
-      <c r="F48" s="65" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="45" t="n"/>
     </row>
     <row r="49" ht="20" customFormat="1" customHeight="1" s="28">
-      <c r="A49" s="73" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>太和</t>
         </is>
       </c>
-      <c r="B49" s="74" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>阜阳太和支行营业室</t>
         </is>
       </c>
-      <c r="C49" s="74" t="n"/>
-      <c r="D49" s="74" t="n"/>
-      <c r="E49" s="75" t="n"/>
-      <c r="F49" s="76" t="n"/>
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="38" t="n"/>
+      <c r="E49" s="46" t="n"/>
+      <c r="F49" s="40" t="n"/>
     </row>
     <row r="50" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A50" s="35" t="n"/>
-      <c r="B50" s="74" t="inlineStr">
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>阜阳太和人民路支行</t>
         </is>
       </c>
-      <c r="C50" s="74" t="n"/>
-      <c r="D50" s="74" t="n"/>
-      <c r="E50" s="75" t="n"/>
-      <c r="F50" s="76" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="38" t="n"/>
+      <c r="E50" s="39" t="n"/>
+      <c r="F50" s="40" t="n"/>
     </row>
     <row r="51" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A51" s="35" t="n"/>
-      <c r="B51" s="74" t="inlineStr">
+      <c r="B51" s="41" t="inlineStr">
         <is>
           <t>阜阳太和大桥支行</t>
         </is>
       </c>
-      <c r="C51" s="74" t="n"/>
-      <c r="D51" s="74" t="n"/>
-      <c r="E51" s="75" t="n"/>
-      <c r="F51" s="76" t="n"/>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="38" t="n"/>
+      <c r="E51" s="39" t="n"/>
+      <c r="F51" s="40" t="n"/>
     </row>
     <row r="52" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A52" s="35" t="n"/>
-      <c r="B52" s="74" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>阜阳太和华源支行</t>
         </is>
       </c>
-      <c r="C52" s="74" t="n"/>
-      <c r="D52" s="74" t="n"/>
-      <c r="E52" s="75" t="n"/>
-      <c r="F52" s="76" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="E52" s="39" t="n"/>
+      <c r="F52" s="40" t="n"/>
     </row>
     <row r="53" ht="20" customFormat="1" customHeight="1" s="28">
       <c r="A53" s="37" t="n"/>
-      <c r="B53" s="62" t="inlineStr">
+      <c r="B53" s="42" t="inlineStr">
         <is>
           <t>小计</t>
         </is>
       </c>
-      <c r="C53" s="63" t="n"/>
-      <c r="D53" s="63" t="n"/>
-      <c r="E53" s="64" t="n"/>
-      <c r="F53" s="65" t="n"/>
+      <c r="C53" s="43" t="n"/>
+      <c r="D53" s="43" t="n"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="45" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="29">
-      <c r="A54" s="74" t="inlineStr">
+      <c r="A54" s="50" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
       <c r="B54" s="34" t="n"/>
-      <c r="C54" s="74" t="n"/>
-      <c r="D54" s="74" t="n"/>
-      <c r="E54" s="75" t="n"/>
-      <c r="F54" s="76" t="n"/>
+      <c r="C54" s="51" t="n"/>
+      <c r="D54" s="51" t="n"/>
+      <c r="E54" s="52" t="n"/>
+      <c r="F54" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
